--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,14 +454,161 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>512.45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>513.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>513.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>515.45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>515.45</v>
+      </c>
+      <c r="E4" t="n">
+        <v>516.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>拍照</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>525.15</v>
-      </c>
-      <c r="E2" t="n">
-        <v>525.65</v>
+      <c r="D5" t="n">
+        <v>517.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>517.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>518.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>518.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>518.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>519.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>763.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>764.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>512.45</v>
+        <v>476.85</v>
       </c>
       <c r="E2" t="n">
-        <v>513.95</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>513.95</v>
+        <v>478.35</v>
       </c>
       <c r="E3" t="n">
-        <v>515.45</v>
+        <v>479.85</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>515.45</v>
+        <v>479.85</v>
       </c>
       <c r="E4" t="n">
-        <v>516.95</v>
+        <v>481.35</v>
       </c>
     </row>
     <row r="5">
@@ -512,19 +512,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>517.25</v>
+        <v>481.35</v>
       </c>
       <c r="E5" t="n">
-        <v>517.75</v>
+        <v>482.85</v>
       </c>
     </row>
     <row r="6">
@@ -533,19 +533,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>517.75</v>
+        <v>510.55</v>
       </c>
       <c r="E6" t="n">
-        <v>518.25</v>
+        <v>512.05</v>
       </c>
     </row>
     <row r="7">
@@ -554,19 +554,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>518.25</v>
+        <v>512.05</v>
       </c>
       <c r="E7" t="n">
-        <v>518.75</v>
+        <v>513.55</v>
       </c>
     </row>
     <row r="8">
@@ -575,19 +575,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>518.75</v>
+        <v>513.55</v>
       </c>
       <c r="E8" t="n">
-        <v>519.25</v>
+        <v>515.05</v>
       </c>
     </row>
     <row r="9">
@@ -596,19 +596,103 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>517.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>517.65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>518.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>518.15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>518.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>518.65</v>
+      </c>
+      <c r="E12" t="n">
+        <v>519.15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>射击</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>763.25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>764.75</v>
+      <c r="D13" t="n">
+        <v>761.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>762.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>478.35</v>
+        <v>479.35</v>
       </c>
       <c r="E3" t="n">
-        <v>479.85</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>479.85</v>
+        <v>481.45</v>
       </c>
       <c r="E4" t="n">
-        <v>481.35</v>
+        <v>482.95</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>481.35</v>
+        <v>490.15</v>
       </c>
       <c r="E5" t="n">
-        <v>482.85</v>
+        <v>491.65</v>
       </c>
     </row>
     <row r="6">
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>512.05</v>
+        <v>511.45</v>
       </c>
       <c r="E7" t="n">
-        <v>513.55</v>
+        <v>512.95</v>
       </c>
     </row>
     <row r="8">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>513.55</v>
+        <v>514.15</v>
       </c>
       <c r="E8" t="n">
-        <v>515.05</v>
+        <v>515.65</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>517.15</v>
+        <v>516.15</v>
       </c>
       <c r="E9" t="n">
         <v>517.65</v>
@@ -622,14 +622,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>517.65</v>
+        <v>761.25</v>
       </c>
       <c r="E10" t="n">
-        <v>518.15</v>
+        <v>762.75</v>
       </c>
     </row>
     <row r="11">
@@ -638,61 +638,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>518.15</v>
+        <v>764.15</v>
       </c>
       <c r="E11" t="n">
-        <v>518.65</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S13</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>拍照</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>518.65</v>
-      </c>
-      <c r="E12" t="n">
-        <v>519.15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>S13</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>761.25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>762.75</v>
+        <v>765.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>479.35</v>
+        <v>477.35</v>
       </c>
       <c r="E3" t="n">
-        <v>480.85</v>
+        <v>478.85</v>
       </c>
     </row>
     <row r="4">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>481.45</v>
+        <v>477.85</v>
       </c>
       <c r="E4" t="n">
-        <v>482.95</v>
+        <v>479.35</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>490.15</v>
+        <v>478.35</v>
       </c>
       <c r="E5" t="n">
-        <v>491.65</v>
+        <v>479.85</v>
       </c>
     </row>
     <row r="6">
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>510.55</v>
+        <v>478.85</v>
       </c>
       <c r="E6" t="n">
-        <v>512.05</v>
+        <v>480.35</v>
       </c>
     </row>
     <row r="7">
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>511.45</v>
+        <v>479.35</v>
       </c>
       <c r="E7" t="n">
-        <v>512.95</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="8">
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>514.15</v>
+        <v>479.85</v>
       </c>
       <c r="E8" t="n">
-        <v>515.65</v>
+        <v>481.35</v>
       </c>
     </row>
     <row r="9">
@@ -596,19 +596,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>516.15</v>
+        <v>480.35</v>
       </c>
       <c r="E9" t="n">
-        <v>517.65</v>
+        <v>481.85</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>761.25</v>
+        <v>480.85</v>
       </c>
       <c r="E10" t="n">
-        <v>762.75</v>
+        <v>482.35</v>
       </c>
     </row>
     <row r="11">
@@ -638,19 +638,355 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>481.35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>482.85</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>S10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>764.15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>765.65</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>510.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>512.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>511.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>512.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>511.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>513.05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>513.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>512.55</v>
+      </c>
+      <c r="E16" t="n">
+        <v>514.05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>513.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>514.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>513.55</v>
+      </c>
+      <c r="E18" t="n">
+        <v>515.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>514.05</v>
+      </c>
+      <c r="E19" t="n">
+        <v>515.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>514.55</v>
+      </c>
+      <c r="E20" t="n">
+        <v>516.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>517.65</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>517.65</v>
+      </c>
+      <c r="E22" t="n">
+        <v>518.15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>518.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>518.65</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>518.65</v>
+      </c>
+      <c r="E24" t="n">
+        <v>519.15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>761.25</v>
+      </c>
+      <c r="E25" t="n">
+        <v>762.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>761.75</v>
+      </c>
+      <c r="E26" t="n">
+        <v>763.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>762.25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>763.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>510.55</v>
+        <v>490.55</v>
       </c>
       <c r="E12" t="n">
-        <v>512.05</v>
+        <v>492.05</v>
       </c>
     </row>
     <row r="13">
@@ -680,7 +680,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>511.05</v>
+        <v>491.05</v>
       </c>
       <c r="E13" t="n">
-        <v>512.55</v>
+        <v>492.55</v>
       </c>
     </row>
     <row r="14">
@@ -701,7 +701,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>511.55</v>
+        <v>491.55</v>
       </c>
       <c r="E14" t="n">
-        <v>513.05</v>
+        <v>493.05</v>
       </c>
     </row>
     <row r="15">
@@ -722,7 +722,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>512.05</v>
+        <v>491.95</v>
       </c>
       <c r="E15" t="n">
-        <v>513.55</v>
+        <v>493.45</v>
       </c>
     </row>
     <row r="16">
@@ -743,7 +743,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>512.55</v>
+        <v>492.45</v>
       </c>
       <c r="E16" t="n">
-        <v>514.05</v>
+        <v>493.95</v>
       </c>
     </row>
     <row r="17">
@@ -764,7 +764,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>513.05</v>
+        <v>492.95</v>
       </c>
       <c r="E17" t="n">
-        <v>514.55</v>
+        <v>494.45</v>
       </c>
     </row>
     <row r="18">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>513.55</v>
+        <v>510.55</v>
       </c>
       <c r="E18" t="n">
-        <v>515.05</v>
+        <v>512.05</v>
       </c>
     </row>
     <row r="19">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>514.05</v>
+        <v>511.05</v>
       </c>
       <c r="E19" t="n">
-        <v>515.55</v>
+        <v>512.55</v>
       </c>
     </row>
     <row r="20">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>514.55</v>
+        <v>511.55</v>
       </c>
       <c r="E20" t="n">
-        <v>516.05</v>
+        <v>513.05</v>
       </c>
     </row>
     <row r="21">
@@ -848,19 +848,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>517.15</v>
+        <v>512.05</v>
       </c>
       <c r="E21" t="n">
-        <v>517.65</v>
+        <v>513.55</v>
       </c>
     </row>
     <row r="22">
@@ -874,14 +874,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>517.65</v>
+        <v>512.55</v>
       </c>
       <c r="E22" t="n">
-        <v>518.15</v>
+        <v>514.05</v>
       </c>
     </row>
     <row r="23">
@@ -890,19 +890,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>518.15</v>
+        <v>513.05</v>
       </c>
       <c r="E23" t="n">
-        <v>518.65</v>
+        <v>514.55</v>
       </c>
     </row>
     <row r="24">
@@ -911,19 +911,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>518.65</v>
+        <v>513.55</v>
       </c>
       <c r="E24" t="n">
-        <v>519.15</v>
+        <v>515.05</v>
       </c>
     </row>
     <row r="25">
@@ -932,7 +932,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>761.25</v>
+        <v>514.05</v>
       </c>
       <c r="E25" t="n">
-        <v>762.75</v>
+        <v>515.55</v>
       </c>
     </row>
     <row r="26">
@@ -953,7 +953,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>761.75</v>
+        <v>514.55</v>
       </c>
       <c r="E26" t="n">
-        <v>763.25</v>
+        <v>516.05</v>
       </c>
     </row>
     <row r="27">
@@ -979,13 +979,139 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>517.15</v>
+      </c>
+      <c r="E27" t="n">
+        <v>517.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>517.65</v>
+      </c>
+      <c r="E28" t="n">
+        <v>518.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>518.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>518.65</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>518.65</v>
+      </c>
+      <c r="E30" t="n">
+        <v>519.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>761.25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>762.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>761.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>763.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>762.25</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E33" t="n">
         <v>763.75</v>
       </c>
     </row>
